--- a/data/hydrophones/tauc50_exceedance.xlsx
+++ b/data/hydrophones/tauc50_exceedance.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\huck4481\Documents\GitHub\hysteresis\data\hydrophones\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nicol\Documents\hysteresis\data\hydrophones\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA67D423-E2CF-4A4F-903D-BC5C68A35929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8A87C5FD-2367-4CAC-96D5-94148CA3EBC6}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8A87C5FD-2367-4CAC-96D5-94148CA3EBC6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
